--- a/Result/profitability/3490.xlsx
+++ b/Result/profitability/3490.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.48</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3975000000000001</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>22.6675</v>
+        <v>20.8775</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.96</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6350000000000001</v>
+        <v>1.20625</v>
       </c>
       <c r="N3" t="n">
-        <v>24.40125</v>
+        <v>23.93</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.54</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7637500000000002</v>
+        <v>1.3425</v>
       </c>
       <c r="N4" t="n">
-        <v>26.2</v>
+        <v>27.93</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8150000000000001</v>
+        <v>1.27125</v>
       </c>
       <c r="N5" t="n">
-        <v>28.4225</v>
+        <v>28.04125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.24</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7312500000000002</v>
+        <v>1.1725</v>
       </c>
       <c r="N6" t="n">
-        <v>27.45125</v>
+        <v>25.05125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6225000000000001</v>
+        <v>1.17875</v>
       </c>
       <c r="N7" t="n">
-        <v>23.435</v>
+        <v>22.7975</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6787500000000001</v>
+        <v>0.9300000000000003</v>
       </c>
       <c r="N8" t="n">
-        <v>24.07125</v>
+        <v>23.3325</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.17</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3537500000000001</v>
+        <v>0.3537500000000002</v>
       </c>
       <c r="N10" t="n">
         <v>24.895</v>
@@ -2026,7 +2026,7 @@
         <v>2.03</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6625000000000001</v>
+        <v>0.6625000000000003</v>
       </c>
       <c r="N13" t="n">
         <v>28.3875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3490</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>72</v>
+      </c>
+      <c r="D75" t="n">
+        <v>62</v>
+      </c>
+      <c r="E75" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-23</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-31.64%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>265</v>
+      </c>
+      <c r="J75" t="n">
+        <v>242</v>
+      </c>
+      <c r="K75" t="n">
+        <v>224</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7225000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.82875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.9710144927536233</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2947630922693267</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>8.488372093023257</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.050000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1774287376381618</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
